--- a/vlearn-app/public/quiz_excel/Day_12_Cloud Services _ Deployment/Day_12_Phan_03_21_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_12_Cloud Services _ Deployment/Day_12_Phan_03_21_Cau.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" s="4" t="n">
         <v>60</v>
@@ -641,7 +641,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đếm kết nối đang mở thay vì chỉ đếm số yêu cầu đã nhận, rồi loại replica không còn healthy.</t>
+          <t>Đối với các kết nối có thời lượng dài và không đồng đều như SSE streaming, thuật toán cân bằng tải phù hợp nhất là Least-Connections (kết hợp lọc sức khỏe replica) thay vì Round-Robin máy móc.</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2,3,5</t>
         </is>
       </c>
       <c r="I4" s="4" t="n">
@@ -696,7 +696,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt khả năng của replica local với khả năng của provider bên ngoài.</t>
+          <t>Với agent I/O-bound nghẽn concurrency và queue: (b) Tín hiệu autoscaling chính là concurrency kéo dài và độ sâu/tuổi của queue, (c) cơ chế cooldown/min/max kèm shedding khi chạm trần, (e) tôn trọng quota downstream của provider và áp dụng concurrency limit toàn cục.</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>60</v>
@@ -744,7 +744,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách khả năng xử lý do mình scale khỏi khả năng do dependency giới hạn.</t>
+          <t>Mở rộng 20 replica với 20 cuộc gọi đồng thời mỗi replica có thể tạo ra 400 in-flight requests, vượt xa quota 100 concurrent calls của provider, dẫn đến tình trạng hàng loạt request bị lỗi 429 Rate Limit.</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1210,7 +1210,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính số request lỗi cho phép và thực tế trên cùng mẫu số.</t>
+          <t>Tổng số 10.000 requests với SLO 99,7% cho phép tối đa: 10.000 * (100% - 99,7%) = 10.000 * 0,003 = 30 request lỗi. Số request lỗi thực tế: 10.000 - 9.950 = 50 request. Số request vượt quá error budget = 50 - 30 = 20 request.</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I16" s="4" t="n">
@@ -1313,7 +1313,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Cần biết inject gì, ở đâu, mong đợi gì và lúc nào dừng.</t>
+          <t>Thí nghiệm Chaos Engineering có kiểm soát đòi hỏi: (a) Giới hạn phạm vi tiêm lỗi (blast radius) tại staging/canary, (b) xác định rõ hành vi kỳ vọng và ngưỡng SLI, (c) thiết lập telemetry đo lường, điều kiện tự động dừng (abort conditions) và kiểm chứng khả năng tự hồi phục.</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
@@ -1368,7 +1368,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn field phục vụ query/trace nhưng không trở thành data exposure.</t>
+          <t>Logging có cấu trúc an toàn trong hệ thống phân tán: (a) Ghi timestamp, event_name, request/trace ID, (b) ghi latency từng chặng, status, số token/cost và error code an toàn, (c) định dạng JSON một dòng và che giấu/bảo vệ dữ liệu định danh người dùng.</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I22" s="4" t="n">
@@ -1615,7 +1615,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Lọc ứng viên không hợp policy trước, rồi mới xét health hoặc chi phí.</t>
+          <t>Quy tắc định tuyến dự phòng (failover routing): (a) Lọc ứng viên theo năng lực kỹ thuật, quy định vùng dữ liệu (data residency), phân quyền và ngân sách trước, (b) chỉ route tới model tương thích hợp đồng API và đang sẵn sàng, (c) trả lỗi có kiểm soát hoặc degraded outcome khi không còn ứng viên hợp lệ.</t>
         </is>
       </c>
     </row>
